--- a/data/raw/devices.xlsx
+++ b/data/raw/devices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxu567\Documents\R\sia.project.1.wd.data\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msa583\Downloads\Relational Database_26-02-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F435131D-66A3-49D7-971B-15B10C3B5B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA25853-2838-4E4D-9119-C07FA75E71EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="247">
   <si>
     <t>device_id</t>
   </si>
@@ -194,6 +194,9 @@
     <t>Clinical</t>
   </si>
   <si>
+    <t>NP</t>
+  </si>
+  <si>
     <t>not allowed to share price details publicly</t>
   </si>
   <si>
@@ -239,7 +242,7 @@
     <t>Finger</t>
   </si>
   <si>
-    <t>sizes4-15</t>
+    <t>sizes 4-15</t>
   </si>
   <si>
     <t>010_sia_wd_min</t>
@@ -342,6 +345,438 @@
   </si>
   <si>
     <t>L41xW35xH10.7</t>
+  </si>
+  <si>
+    <t>016_sia_wd_app</t>
+  </si>
+  <si>
+    <t>Apple Watch Series 8</t>
+  </si>
+  <si>
+    <t>https://support.apple.com/en-us/111848</t>
+  </si>
+  <si>
+    <t>L45xW38xH10.7</t>
+  </si>
+  <si>
+    <t>017_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>BIOPAC</t>
+  </si>
+  <si>
+    <t>Research Ring</t>
+  </si>
+  <si>
+    <t>https://www.biopac.com/product/research-ring/</t>
+  </si>
+  <si>
+    <t>one-time purchase price of a device, option to interface up to 9 rings with AcqKnowledge Ring software (€5284)</t>
+  </si>
+  <si>
+    <t>sizes 6-13</t>
+  </si>
+  <si>
+    <t>018_sia_wd_now</t>
+  </si>
+  <si>
+    <t>NOWATCH</t>
+  </si>
+  <si>
+    <t>https://nowatch.com/</t>
+  </si>
+  <si>
+    <t>D37xH10.9</t>
+  </si>
+  <si>
+    <t>019_sia_wd_goo</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Pixel Watch 1</t>
+  </si>
+  <si>
+    <t>https://store.google.com/gb/config/google_pixel_watch?hl=en-GB&amp;selections=eyJwcm9kdWN0RmFtaWx5IjoiWjI5dloyeGxYM0JwZUdWc1gzZGhkR05vIn0%3D</t>
+  </si>
+  <si>
+    <t>D41xH12.3</t>
+  </si>
+  <si>
+    <t>020_sia_wd_goo</t>
+  </si>
+  <si>
+    <t>Pixel Watch 2</t>
+  </si>
+  <si>
+    <t>https://store.google.com/nl/product/pixel_watch_2?hl=nl</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Some features require Fitbit Premium (first 6 months free, after that 8.99EUR a month or 79.99EUR yearly)</t>
+  </si>
+  <si>
+    <t>021_sia_wd_cor</t>
+  </si>
+  <si>
+    <t>Corsano</t>
+  </si>
+  <si>
+    <t>Corsano Cardiowatch 287-2</t>
+  </si>
+  <si>
+    <t>https://corsano.com/shop/</t>
+  </si>
+  <si>
+    <t>the price includes the watch, a blood pressure cuff, and platform access for 1 month - note that portal setup and configuration always comes with a one-off 2000 euro payment- subscription to the portal for a single bracelet over a year is 600 euros</t>
+  </si>
+  <si>
+    <t>L25xW40xH10</t>
+  </si>
+  <si>
+    <t>022_sia_wd_cor</t>
+  </si>
+  <si>
+    <t>Corsano Cardiowatch 287-1</t>
+  </si>
+  <si>
+    <t>Flexible</t>
+  </si>
+  <si>
+    <t>L36xW25xH9</t>
+  </si>
+  <si>
+    <t>023_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>Biospace Inc.</t>
+  </si>
+  <si>
+    <t>InBody BAND 2</t>
+  </si>
+  <si>
+    <t>https://inbodyusa.com/products/band2/</t>
+  </si>
+  <si>
+    <t>L25.4xW17.78xH10.16</t>
+  </si>
+  <si>
+    <t>024_sia_wd_fit</t>
+  </si>
+  <si>
+    <t>Sense</t>
+  </si>
+  <si>
+    <t>https://www.fitbit.com/global/us/products/smartwatches/sense</t>
+  </si>
+  <si>
+    <t>Some features require a subscription app (first 6 months free, after that 8.99EUR a month or 79.99EUR yearly)</t>
+  </si>
+  <si>
+    <t>L40.4xW40.4xH12.4</t>
+  </si>
+  <si>
+    <t>025_sia_wd_fit</t>
+  </si>
+  <si>
+    <t>Sense 2</t>
+  </si>
+  <si>
+    <t>https://www.fitbit.com/global/us/products/smartwatches/sense2?sku=521BKGB</t>
+  </si>
+  <si>
+    <t>L40.5xW40.5xH12.3</t>
+  </si>
+  <si>
+    <t>026_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>Garmin</t>
+  </si>
+  <si>
+    <t>vivoactive 4</t>
+  </si>
+  <si>
+    <t>https://www.garmin.com/en-US/p/643382</t>
+  </si>
+  <si>
+    <t>D40xH12.7</t>
+  </si>
+  <si>
+    <t>027_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>vivoactive 5</t>
+  </si>
+  <si>
+    <t>https://www.garmin.com/en-US/p/1057989#specs</t>
+  </si>
+  <si>
+    <t>D42.2xH11.1</t>
+  </si>
+  <si>
+    <t>028_sia_wd_who</t>
+  </si>
+  <si>
+    <t>WHOOP</t>
+  </si>
+  <si>
+    <t>WHOOP 4.0</t>
+  </si>
+  <si>
+    <t>https://www.whoop.com/</t>
+  </si>
+  <si>
+    <t>monthly subscription for a device</t>
+  </si>
+  <si>
+    <t>Adjustable strap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L43.18XW27.9XH10.16 </t>
+  </si>
+  <si>
+    <t>029_sia_wd_who</t>
+  </si>
+  <si>
+    <t>WHOOP 3.0</t>
+  </si>
+  <si>
+    <t>https://shop.whoop.com/en-eu/collections/whoop3-0</t>
+  </si>
+  <si>
+    <t>L43.18XW27.9XH10.17</t>
+  </si>
+  <si>
+    <t>030_sia_wd_cir</t>
+  </si>
+  <si>
+    <t>Circular</t>
+  </si>
+  <si>
+    <t>Circular Slim</t>
+  </si>
+  <si>
+    <t>https://www.circular.xyz/</t>
+  </si>
+  <si>
+    <t>sizes 4-16</t>
+  </si>
+  <si>
+    <t>031_sia_wd_mov</t>
+  </si>
+  <si>
+    <t>movisens</t>
+  </si>
+  <si>
+    <t>EcgMove4</t>
+  </si>
+  <si>
+    <t>https://www.movisens.com/en/products/ecg-sensor/</t>
+  </si>
+  <si>
+    <t>Includes the CPU and one chest belt</t>
+  </si>
+  <si>
+    <t>L11.5XW62.3XH38.6</t>
+  </si>
+  <si>
+    <t>032_sia_wd_wit</t>
+  </si>
+  <si>
+    <t>Withings</t>
+  </si>
+  <si>
+    <t>Scanwatch</t>
+  </si>
+  <si>
+    <t>https://www.withings.com/eu/en/scanwatch-2</t>
+  </si>
+  <si>
+    <t>D38xH13.2</t>
+  </si>
+  <si>
+    <t>033_sia_wd_wit</t>
+  </si>
+  <si>
+    <t>Scanwatch 2</t>
+  </si>
+  <si>
+    <t>D38.4xH13.4</t>
+  </si>
+  <si>
+    <t>034_sia_wd_spa</t>
+  </si>
+  <si>
+    <t>Spacelabs</t>
+  </si>
+  <si>
+    <t>OnTrak</t>
+  </si>
+  <si>
+    <t>https://spacelabshealthcare.com/products/diagnostic-cardiology/abp-monitoring/ontrak/</t>
+  </si>
+  <si>
+    <t>L10.15xH2.76xW7.0</t>
+  </si>
+  <si>
+    <t>035_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>Vivosmart 5</t>
+  </si>
+  <si>
+    <t>https://www.garmin.com/en-US/p/782585/</t>
+  </si>
+  <si>
+    <t>L19.5xW10.7xH217 </t>
+  </si>
+  <si>
+    <t>036_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>Vivosmart 4</t>
+  </si>
+  <si>
+    <t>https://www.garmin.com/en-US/p/605739/</t>
+  </si>
+  <si>
+    <t>L15xW10.5xH197</t>
+  </si>
+  <si>
+    <t>037_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>Index BPM Smart Blood Pressure</t>
+  </si>
+  <si>
+    <t>https://www.garmin.com/en-US/p/716808/</t>
+  </si>
+  <si>
+    <t>Upper arm</t>
+  </si>
+  <si>
+    <t>L58xW145xH47</t>
+  </si>
+  <si>
+    <t>038_sia_wd_sky</t>
+  </si>
+  <si>
+    <t>SkyLabs</t>
+  </si>
+  <si>
+    <t>CART BP</t>
+  </si>
+  <si>
+    <t>https://www.skylabs.io/en</t>
+  </si>
+  <si>
+    <t>Clinical &amp; Consumer</t>
+  </si>
+  <si>
+    <t>039_sia_wd_ama</t>
+  </si>
+  <si>
+    <t>Amazfit</t>
+  </si>
+  <si>
+    <t>Helio Ring</t>
+  </si>
+  <si>
+    <t>https://us.amazfit.com/products/amazfit-helio-ring</t>
+  </si>
+  <si>
+    <t>sizes 8, 10, 12</t>
+  </si>
+  <si>
+    <t>040_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>BioStrap</t>
+  </si>
+  <si>
+    <t>Biostrap Kairos</t>
+  </si>
+  <si>
+    <t>https://shop.biostrap.com/products/biostrap-kairos-pilot-set</t>
+  </si>
+  <si>
+    <t>L36xW22xH12.5</t>
+  </si>
+  <si>
+    <t>041_sia_wd_car</t>
+  </si>
+  <si>
+    <t>CardioMood</t>
+  </si>
+  <si>
+    <t>CardioMood 287-2</t>
+  </si>
+  <si>
+    <t>https://cardiomood.com/product/cardiowatch-287-2</t>
+  </si>
+  <si>
+    <t>Wrist strap</t>
+  </si>
+  <si>
+    <t>40Lx25Hx10W</t>
+  </si>
+  <si>
+    <t>042_sia_wd_sam</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>Galaxy Ring</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/us/rings/galaxy-ring/</t>
+  </si>
+  <si>
+    <t>sizes 5-15</t>
+  </si>
+  <si>
+    <t>043_sia_wd_goo</t>
+  </si>
+  <si>
+    <t>Pixel Watch 3</t>
+  </si>
+  <si>
+    <t>https://store.google.com/product/pixel_watch_3?hl=nl</t>
+  </si>
+  <si>
+    <t>044_sia_wd_adi</t>
+  </si>
+  <si>
+    <t>AD Instruments</t>
+  </si>
+  <si>
+    <t>Equivital eq02+ Lifemonitor</t>
+  </si>
+  <si>
+    <t>https://equivital.com/products/eq02-lifemonitor</t>
+  </si>
+  <si>
+    <t>78x55x11</t>
+  </si>
+  <si>
+    <t>045_sia_wd_med</t>
+  </si>
+  <si>
+    <t>Medtronic Zephyr</t>
+  </si>
+  <si>
+    <t>BioHarness 3.0</t>
+  </si>
+  <si>
+    <t>https://www.zephyranywhere.com/system/overview</t>
+  </si>
+  <si>
+    <t>Including biomodule, one charger and a strap; optionally add GPS for 190 and GPS charger 5 bay for 340, gateway for live monitoring 450; Omnisense software 4530, and SDK kit for downloading and streaming and matlab script 170; all excluding VAT</t>
+  </si>
+  <si>
+    <t>28Dx7H</t>
   </si>
 </sst>
 </file>
@@ -351,12 +786,24 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -385,17 +832,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -417,6 +853,25 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -441,21 +896,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -466,29 +918,53 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{F3EA98DD-C3F0-4B24-BF54-1B45469318BB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -766,23 +1242,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M46"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="38.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="12" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="12" width="17.5703125" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="12"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" customWidth="1"/>
+    <col min="4" max="4" width="38.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="22.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="10" max="12" width="17.5546875" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -792,7 +1268,7 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -823,7 +1299,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -839,32 +1315,32 @@
       <c r="E2" s="1">
         <v>42005</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="23">
         <v>1542</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="23">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -880,39 +1356,39 @@
       <c r="E3" s="1">
         <v>43831</v>
       </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F3" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="23">
         <v>1984</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="23">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -921,36 +1397,37 @@
       <c r="E4" s="1">
         <v>39083</v>
       </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>4550</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="22"/>
+      <c r="J4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="13">
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -959,39 +1436,39 @@
       <c r="E5" s="1">
         <v>45352</v>
       </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F5" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>5995</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="13">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1000,36 +1477,37 @@
       <c r="E6" s="1">
         <v>44440</v>
       </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F6" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="14">
         <v>150</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="I6" s="22"/>
+      <c r="J6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="5" t="s">
         <v>46</v>
       </c>
       <c r="M6" s="14">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1038,38 +1516,40 @@
       <c r="E7" s="1">
         <v>43466</v>
       </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="F7" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" t="s">
+      <c r="H7" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="I7" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="15">
+      <c r="L7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="13">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>55</v>
+      <c r="C8" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>50</v>
@@ -1077,38 +1557,40 @@
       <c r="E8" s="1">
         <v>43466</v>
       </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="F8" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" t="s">
+      <c r="H8" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="I8" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="15">
+      <c r="L8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="13">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="7" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>58</v>
+      <c r="C9" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>50</v>
@@ -1116,314 +1598,1496 @@
       <c r="E9" s="1">
         <v>44682</v>
       </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F9" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" t="s">
+      <c r="H9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="I9" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" s="15">
+      <c r="L9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="13">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1">
         <v>44501</v>
       </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F10" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <v>314</v>
       </c>
-      <c r="I10" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="I10" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="J10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M10" s="15">
+      <c r="L10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="9" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>70</v>
       </c>
+      <c r="C11" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1">
         <v>41640</v>
       </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="F11" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>5499</v>
       </c>
-      <c r="I11" t="s">
-        <v>72</v>
-      </c>
-      <c r="J11" s="4" t="s">
+      <c r="I11" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="15">
+      <c r="L11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="M11" s="13">
         <v>370</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>76</v>
       </c>
+      <c r="C12" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="D12" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12" s="1">
         <v>43831</v>
       </c>
-      <c r="F12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="F12" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H12" s="14">
         <v>2000</v>
       </c>
-      <c r="I12" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="I12" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="J12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>80</v>
+      <c r="L12" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="M12" s="14">
         <v>195</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="7" t="s">
+    <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>83</v>
       </c>
+      <c r="C13" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="D13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E13" s="1">
         <v>43466</v>
       </c>
-      <c r="F13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" t="s">
-        <v>85</v>
+      <c r="F13" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>86</v>
       </c>
       <c r="H13" s="14">
         <v>600</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="I13" s="22"/>
+      <c r="J13" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="L13" s="5" t="s">
-        <v>87</v>
+      <c r="L13" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="M13" s="14">
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="7" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="C14" s="5" t="s">
         <v>91</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="E14" s="1">
         <v>44075</v>
       </c>
-      <c r="F14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="F14" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H14" s="14">
         <v>240</v>
       </c>
-      <c r="I14" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="4" t="s">
+      <c r="I14" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>93</v>
+      <c r="L14" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="M14" s="14">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="7" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="B15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>96</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>97</v>
       </c>
       <c r="E15" s="1">
         <v>45170</v>
       </c>
-      <c r="F15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="F15" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="14">
         <v>899</v>
       </c>
-      <c r="I15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J15" s="4" t="s">
+      <c r="I15" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="4" t="s">
-        <v>97</v>
+      <c r="L15" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="M15" s="14">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="B16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>100</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="E16" s="1">
         <v>45170</v>
       </c>
-      <c r="F16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="F16" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H16" s="14">
         <v>449</v>
       </c>
-      <c r="I16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="I16" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="4" t="s">
-        <v>101</v>
+      <c r="L16" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="M16" s="14">
         <v>32</v>
       </c>
     </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="1">
+        <v>44805</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="23">
+        <v>400</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="M17" s="23">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="1">
+        <v>45108</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="23">
+        <v>2020</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M18" s="23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="1">
+        <v>44927</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="23">
+        <v>450</v>
+      </c>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="M19" s="23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="1">
+        <v>44835</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="23">
+        <v>325</v>
+      </c>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="M20" s="23">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" s="1">
+        <v>45200</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="23">
+        <v>399</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="M21" s="23">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="1">
+        <v>44835</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" s="23">
+        <v>1080</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="M22" s="23">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="1">
+        <v>44501</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="M23" s="23">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="1">
+        <v>42979</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="23">
+        <v>149</v>
+      </c>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="M24" s="23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="24">
+        <v>44075</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="18">
+        <v>150</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="M25" s="23">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="24">
+        <v>44805</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="23">
+        <v>223</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="M26" s="23">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="1">
+        <v>43709</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="10">
+        <v>299</v>
+      </c>
+      <c r="J27" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="M27" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E28" s="1">
+        <v>45170</v>
+      </c>
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="10">
+        <v>300</v>
+      </c>
+      <c r="J28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="M28" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" s="24">
+        <v>44440</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="23">
+        <v>30</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="M29" s="23">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="E30" s="1">
+        <v>43466</v>
+      </c>
+      <c r="F30" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="23">
+        <v>30</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="J30" t="s">
+        <v>164</v>
+      </c>
+      <c r="K30" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="M30" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" s="1">
+        <v>45261</v>
+      </c>
+      <c r="F31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H31" s="10">
+        <v>263</v>
+      </c>
+      <c r="J31" t="s">
+        <v>66</v>
+      </c>
+      <c r="K31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L31" t="s">
+        <v>174</v>
+      </c>
+      <c r="M31" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" t="s">
+        <v>178</v>
+      </c>
+      <c r="E32" s="1">
+        <v>44197</v>
+      </c>
+      <c r="F32" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="10">
+        <v>2089</v>
+      </c>
+      <c r="I32" t="s">
+        <v>179</v>
+      </c>
+      <c r="J32" t="s">
+        <v>80</v>
+      </c>
+      <c r="K32" t="s">
+        <v>39</v>
+      </c>
+      <c r="L32" t="s">
+        <v>180</v>
+      </c>
+      <c r="M32" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="1">
+        <v>44501</v>
+      </c>
+      <c r="F33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" s="10">
+        <v>299.95</v>
+      </c>
+      <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" t="s">
+        <v>185</v>
+      </c>
+      <c r="M33" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E34" s="1">
+        <v>45200</v>
+      </c>
+      <c r="F34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" s="10">
+        <v>349.95</v>
+      </c>
+      <c r="J34" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" t="s">
+        <v>188</v>
+      </c>
+      <c r="M34" s="10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="1">
+        <v>43466</v>
+      </c>
+      <c r="F35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="10">
+        <v>3249</v>
+      </c>
+      <c r="J35" t="s">
+        <v>80</v>
+      </c>
+      <c r="K35" t="s">
+        <v>35</v>
+      </c>
+      <c r="L35" t="s">
+        <v>193</v>
+      </c>
+      <c r="M35" s="10">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" t="s">
+        <v>196</v>
+      </c>
+      <c r="E36" s="1">
+        <v>44652</v>
+      </c>
+      <c r="F36" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="10">
+        <v>150</v>
+      </c>
+      <c r="J36" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" t="s">
+        <v>197</v>
+      </c>
+      <c r="M36" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B37" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" t="s">
+        <v>200</v>
+      </c>
+      <c r="E37" s="1">
+        <v>43344</v>
+      </c>
+      <c r="F37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" s="10">
+        <v>150</v>
+      </c>
+      <c r="J37" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" t="s">
+        <v>201</v>
+      </c>
+      <c r="M37" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" s="1">
+        <v>44805</v>
+      </c>
+      <c r="F38" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" t="s">
+        <v>45</v>
+      </c>
+      <c r="H38" s="10">
+        <v>176</v>
+      </c>
+      <c r="J38" t="s">
+        <v>80</v>
+      </c>
+      <c r="K38" t="s">
+        <v>205</v>
+      </c>
+      <c r="L38" t="s">
+        <v>206</v>
+      </c>
+      <c r="M38" s="10">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" t="s">
+        <v>208</v>
+      </c>
+      <c r="C39" t="s">
+        <v>209</v>
+      </c>
+      <c r="D39" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" s="1">
+        <v>44986</v>
+      </c>
+      <c r="F39" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" t="s">
+        <v>211</v>
+      </c>
+      <c r="H39" s="10">
+        <v>447</v>
+      </c>
+      <c r="J39" t="s">
+        <v>66</v>
+      </c>
+      <c r="K39" t="s">
+        <v>67</v>
+      </c>
+      <c r="L39" t="s">
+        <v>52</v>
+      </c>
+      <c r="M39" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B40" t="s">
+        <v>213</v>
+      </c>
+      <c r="C40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D40" t="s">
+        <v>215</v>
+      </c>
+      <c r="E40" s="1">
+        <v>45413</v>
+      </c>
+      <c r="F40" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" t="s">
+        <v>45</v>
+      </c>
+      <c r="H40" s="10">
+        <v>300</v>
+      </c>
+      <c r="J40" t="s">
+        <v>66</v>
+      </c>
+      <c r="K40" t="s">
+        <v>67</v>
+      </c>
+      <c r="L40" t="s">
+        <v>216</v>
+      </c>
+      <c r="M40" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B41" t="s">
+        <v>218</v>
+      </c>
+      <c r="C41" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E41" s="1">
+        <v>45108</v>
+      </c>
+      <c r="F41" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="10">
+        <v>275</v>
+      </c>
+      <c r="J41" t="s">
+        <v>164</v>
+      </c>
+      <c r="K41" t="s">
+        <v>134</v>
+      </c>
+      <c r="L41" t="s">
+        <v>221</v>
+      </c>
+      <c r="M41" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" t="s">
+        <v>223</v>
+      </c>
+      <c r="C42" t="s">
+        <v>224</v>
+      </c>
+      <c r="D42" t="s">
+        <v>225</v>
+      </c>
+      <c r="E42" s="1">
+        <v>44927</v>
+      </c>
+      <c r="F42" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42" s="10">
+        <v>499</v>
+      </c>
+      <c r="J42" t="s">
+        <v>226</v>
+      </c>
+      <c r="K42" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" t="s">
+        <v>227</v>
+      </c>
+      <c r="M42" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B43" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" t="s">
+        <v>230</v>
+      </c>
+      <c r="D43" t="s">
+        <v>231</v>
+      </c>
+      <c r="E43" s="1">
+        <v>45505</v>
+      </c>
+      <c r="F43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" t="s">
+        <v>45</v>
+      </c>
+      <c r="H43" s="10">
+        <v>449</v>
+      </c>
+      <c r="J43" t="s">
+        <v>66</v>
+      </c>
+      <c r="K43" t="s">
+        <v>67</v>
+      </c>
+      <c r="L43" t="s">
+        <v>232</v>
+      </c>
+      <c r="M43" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" t="s">
+        <v>234</v>
+      </c>
+      <c r="D44" t="s">
+        <v>235</v>
+      </c>
+      <c r="E44" s="1">
+        <v>45292</v>
+      </c>
+      <c r="F44" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="10">
+        <v>399</v>
+      </c>
+      <c r="J44" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" t="s">
+        <v>121</v>
+      </c>
+      <c r="M44" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B45" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="1">
+        <v>44197</v>
+      </c>
+      <c r="F45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="10">
+        <v>1977</v>
+      </c>
+      <c r="J45" t="s">
+        <v>87</v>
+      </c>
+      <c r="K45" t="s">
+        <v>39</v>
+      </c>
+      <c r="L45" t="s">
+        <v>240</v>
+      </c>
+      <c r="M45" s="10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B46" t="s">
+        <v>242</v>
+      </c>
+      <c r="C46" t="s">
+        <v>243</v>
+      </c>
+      <c r="D46" t="s">
+        <v>244</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46" s="10">
+        <v>766</v>
+      </c>
+      <c r="I46" t="s">
+        <v>245</v>
+      </c>
+      <c r="J46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K46" t="s">
+        <v>39</v>
+      </c>
+      <c r="L46" t="s">
+        <v>246</v>
+      </c>
+      <c r="M46" s="10">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Size " prompt="Device dimensions (mm) using:_x000a_Length x Width x Height or Diameter x Height for round objects - the first letters are used to denote specific dimensions (e.g., L36xW21xH30).  Rings are presented using the US ring sizes system (e.g., sizes4-10)" sqref="L17 L19:L30" xr:uid="{19B59255-799B-417A-93BB-2CDE1B702B13}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Device costs" prompt="One-time purchase price; if applicable, additional/hidden costs (e.g., subscription, software needed to operate the device, discount options, etc.)." sqref="I21:I22 H25:I25 I26 I29:I30" xr:uid="{32E813C5-98A7-4200-9207-8AAB91F228A6}"/>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{F7BC6317-11D5-4DB6-91CA-D296F113E276}"/>
     <hyperlink ref="D4" r:id="rId2" xr:uid="{05A7A3C7-20E5-4EE9-A558-26A53BB5FD81}"/>
@@ -1440,23 +3104,28 @@
     <hyperlink ref="D15" r:id="rId13" xr:uid="{00102010-2903-4342-B3DB-A70071E28C67}"/>
     <hyperlink ref="D16" r:id="rId14" xr:uid="{0E478E70-C250-40ED-8117-4DFEFD1277BC}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{6BC84695-FBBA-4C50-BF1C-FE071E3C4132}"/>
+    <hyperlink ref="D41" r:id="rId16" xr:uid="{EE67E8DD-5D02-4056-8EE6-FD0C2218739A}"/>
+    <hyperlink ref="D17" r:id="rId17" xr:uid="{07352B8B-B049-47A5-81B7-68CB0C888470}"/>
+    <hyperlink ref="D18" r:id="rId18" xr:uid="{C2AC64DC-149D-49E8-9BEF-7A1E7BB6F2F6}"/>
+    <hyperlink ref="D19" r:id="rId19" xr:uid="{62598EE7-CFD9-49F0-9F01-E9E6CBD7D45D}"/>
+    <hyperlink ref="D20" r:id="rId20" xr:uid="{6D82FF17-5774-47CD-BFD5-F0C7F20590F0}"/>
+    <hyperlink ref="D21" r:id="rId21" xr:uid="{5AB8D86A-E83F-48B5-A4C4-4A37F010A655}"/>
+    <hyperlink ref="D22" r:id="rId22" xr:uid="{56C98081-B8E3-4467-AF60-6BBDC294D945}"/>
+    <hyperlink ref="D23" r:id="rId23" xr:uid="{5EDB474A-7E24-429A-B97B-D67F383FB3BC}"/>
+    <hyperlink ref="D24" r:id="rId24" xr:uid="{15CCA45C-FCD2-4586-AF1F-001212E8406B}"/>
+    <hyperlink ref="D25" r:id="rId25" xr:uid="{BD86063C-78A6-4429-AC2B-59E2AA4B0359}"/>
+    <hyperlink ref="D26" r:id="rId26" xr:uid="{4EAA1B14-65F3-4B27-865A-3B0B7BE12B7A}"/>
+    <hyperlink ref="D27" r:id="rId27" xr:uid="{18CD6020-4C1B-4175-9537-4F7F668030A8}"/>
+    <hyperlink ref="D28" r:id="rId28" location="specs" xr:uid="{D5D1B5BE-74C3-4D63-8CC2-ABA43A144944}"/>
+    <hyperlink ref="D29" r:id="rId29" xr:uid="{B55B89B9-EE17-4568-B492-27676E659FF4}"/>
+    <hyperlink ref="D30" r:id="rId30" xr:uid="{FA4DF66A-2244-4684-8859-16AF8E74A222}"/>
+    <hyperlink ref="D31" r:id="rId31" xr:uid="{7F121914-5537-45E6-A95D-B4764A311F26}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1465,9 +3134,9 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006131D81E7FE36E44885B3A04523FCF5D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3c9ab67dcfa560232a36bfe42a1cf3da">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71842362-ab5d-46b4-b35f-08dc9c6328ce" xmlns:ns3="8def90a7-5747-4395-b698-a599996d7912" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="85c6a7f5c224f550ecad7291476c1ef0" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006131D81E7FE36E44885B3A04523FCF5D" ma:contentTypeVersion="14" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8f9efaeda295997044994eea58453835">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71842362-ab5d-46b4-b35f-08dc9c6328ce" xmlns:ns3="8def90a7-5747-4395-b698-a599996d7912" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7a2e7ed8b28d563a97a27396956f6ac0" ns2:_="" ns3:_="">
     <xsd:import namespace="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
     <xsd:import namespace="8def90a7-5747-4395-b698-a599996d7912"/>
     <xsd:element name="properties">
@@ -1514,7 +3183,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="eaf58ba8-1e8d-4aec-a6f5-993f6032dc74" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Afbeeldingtags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="eaf58ba8-1e8d-4aec-a6f5-993f6032dc74" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1568,7 +3237,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Gedeeld met" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1587,7 +3256,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Gedeeld met details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -1604,8 +3273,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhoudstype"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1694,24 +3363,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C39BF036-B4AC-4393-9990-793AE5FB9BA5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7D8E78A-C06A-41E3-81BB-050BD45B738F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1719,8 +3382,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29494E9F-D417-4C02-8DEE-33154BA4BF6D}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C71B4682-7187-48E0-9E57-1CE0A2072E2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1736,4 +3399,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C39BF036-B4AC-4393-9990-793AE5FB9BA5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
+    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/devices.xlsx
+++ b/data/raw/devices.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msa583\Downloads\Relational Database_26-02-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxu567\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA25853-2838-4E4D-9119-C07FA75E71EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55123604-21BE-4A85-90B5-58E0D466DF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="290">
   <si>
     <t>device_id</t>
   </si>
@@ -777,6 +777,135 @@
   </si>
   <si>
     <t>28Dx7H</t>
+  </si>
+  <si>
+    <t>046_sia_wd_rin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RingConn </t>
+  </si>
+  <si>
+    <t>RingConn Gen2</t>
+  </si>
+  <si>
+    <t>https://ringconn.com/products/ringconn-gen-2?variant=48162846769460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer </t>
+  </si>
+  <si>
+    <t>sizes 6-14</t>
+  </si>
+  <si>
+    <t>047_sia_wd_ult</t>
+  </si>
+  <si>
+    <t>Ultrahuman</t>
+  </si>
+  <si>
+    <t>Ultrahuman Ring AIR</t>
+  </si>
+  <si>
+    <t>https://www.ultrahuman.com/</t>
+  </si>
+  <si>
+    <t>sizes 5-14</t>
+  </si>
+  <si>
+    <t>048_sia_wd_nua</t>
+  </si>
+  <si>
+    <t>Nuanic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuanic Ring </t>
+  </si>
+  <si>
+    <t>https://nuanic.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research </t>
+  </si>
+  <si>
+    <t>price depends on the number of rings ordered; mobile app, access to raw data, 12 months of complimentary Nuanic Cloud and dedicated technical support is included</t>
+  </si>
+  <si>
+    <t>sizes 7, 9, 10, 12</t>
+  </si>
+  <si>
+    <t>049_sia_wd_cos</t>
+  </si>
+  <si>
+    <t>Cosinuss</t>
+  </si>
+  <si>
+    <t>c-med alpha</t>
+  </si>
+  <si>
+    <t>https://www.cosinuss.com/en/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical </t>
+  </si>
+  <si>
+    <t>Earable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ear </t>
+  </si>
+  <si>
+    <t>L55.2xH58.6xH10.0</t>
+  </si>
+  <si>
+    <t>050_sia_wd_lum</t>
+  </si>
+  <si>
+    <t>Lumia Health</t>
+  </si>
+  <si>
+    <t>Lumia</t>
+  </si>
+  <si>
+    <t>https://lumiahealth.com/</t>
+  </si>
+  <si>
+    <t>Upcoming</t>
+  </si>
+  <si>
+    <t>plus a subscription cost of 16.58 per month for a yearly subscription</t>
+  </si>
+  <si>
+    <t>051_sia_wd_plu</t>
+  </si>
+  <si>
+    <t>Plux</t>
+  </si>
+  <si>
+    <t>BioSignal kit</t>
+  </si>
+  <si>
+    <t>https://www.pluxbiosignals.com/products/4-channel-biosignals-kit</t>
+  </si>
+  <si>
+    <t>4-Channel biosignalsplux Kit costs 2359.50euro when bought separately. When combined in a kit builder set, the 4-channel kit costs 1950.00euro, where sensors with varying prices can be added; an example is given using ECG, EMC, EDA and accelerometer sensors. Extra costs for add-on software packages are applicable (e.g., 598.95euro)</t>
+  </si>
+  <si>
+    <t>54Hx85Lx10W</t>
+  </si>
+  <si>
+    <t>052_sia_wd_plu</t>
+  </si>
+  <si>
+    <t>respiBAN BLE</t>
+  </si>
+  <si>
+    <t>https://www.pluxbiosignals.com/collections/research-kits/products/respiban-ble</t>
+  </si>
+  <si>
+    <t>additional costs for analyses software for parameter extraction costs 598.95euro</t>
+  </si>
+  <si>
+    <t>31Hx71Lx11W</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
@@ -3080,6 +3209,284 @@
       </c>
       <c r="M46" s="10">
         <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>247</v>
+      </c>
+      <c r="B47" t="s">
+        <v>248</v>
+      </c>
+      <c r="C47" t="s">
+        <v>249</v>
+      </c>
+      <c r="D47" t="s">
+        <v>250</v>
+      </c>
+      <c r="E47" s="1">
+        <v>45505</v>
+      </c>
+      <c r="F47" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" t="s">
+        <v>251</v>
+      </c>
+      <c r="H47" s="10">
+        <v>275</v>
+      </c>
+      <c r="J47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K47" t="s">
+        <v>67</v>
+      </c>
+      <c r="L47" t="s">
+        <v>252</v>
+      </c>
+      <c r="M47" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>253</v>
+      </c>
+      <c r="B48" t="s">
+        <v>254</v>
+      </c>
+      <c r="C48" t="s">
+        <v>255</v>
+      </c>
+      <c r="D48" t="s">
+        <v>256</v>
+      </c>
+      <c r="E48" s="1">
+        <v>44927</v>
+      </c>
+      <c r="F48" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" s="10">
+        <v>379</v>
+      </c>
+      <c r="J48" t="s">
+        <v>66</v>
+      </c>
+      <c r="K48" t="s">
+        <v>67</v>
+      </c>
+      <c r="L48" t="s">
+        <v>257</v>
+      </c>
+      <c r="M48" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>258</v>
+      </c>
+      <c r="B49" t="s">
+        <v>259</v>
+      </c>
+      <c r="C49" t="s">
+        <v>260</v>
+      </c>
+      <c r="D49" t="s">
+        <v>261</v>
+      </c>
+      <c r="E49" s="1">
+        <v>45017</v>
+      </c>
+      <c r="F49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" t="s">
+        <v>262</v>
+      </c>
+      <c r="H49" s="10">
+        <v>650</v>
+      </c>
+      <c r="I49" t="s">
+        <v>263</v>
+      </c>
+      <c r="J49" t="s">
+        <v>66</v>
+      </c>
+      <c r="K49" t="s">
+        <v>67</v>
+      </c>
+      <c r="L49" t="s">
+        <v>264</v>
+      </c>
+      <c r="M49" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>265</v>
+      </c>
+      <c r="B50" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" t="s">
+        <v>267</v>
+      </c>
+      <c r="D50" t="s">
+        <v>268</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" t="s">
+        <v>269</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J50" t="s">
+        <v>270</v>
+      </c>
+      <c r="K50" t="s">
+        <v>271</v>
+      </c>
+      <c r="L50" t="s">
+        <v>272</v>
+      </c>
+      <c r="M50" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>273</v>
+      </c>
+      <c r="B51" t="s">
+        <v>274</v>
+      </c>
+      <c r="C51" t="s">
+        <v>275</v>
+      </c>
+      <c r="D51" t="s">
+        <v>276</v>
+      </c>
+      <c r="E51" s="1">
+        <v>45658</v>
+      </c>
+      <c r="F51" t="s">
+        <v>277</v>
+      </c>
+      <c r="G51" t="s">
+        <v>251</v>
+      </c>
+      <c r="H51" s="10">
+        <v>379</v>
+      </c>
+      <c r="I51" t="s">
+        <v>278</v>
+      </c>
+      <c r="J51" t="s">
+        <v>270</v>
+      </c>
+      <c r="K51" t="s">
+        <v>271</v>
+      </c>
+      <c r="L51" t="s">
+        <v>52</v>
+      </c>
+      <c r="M51" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>279</v>
+      </c>
+      <c r="B52" t="s">
+        <v>280</v>
+      </c>
+      <c r="C52" t="s">
+        <v>281</v>
+      </c>
+      <c r="D52" t="s">
+        <v>282</v>
+      </c>
+      <c r="E52" s="1">
+        <v>45383</v>
+      </c>
+      <c r="F52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" t="s">
+        <v>262</v>
+      </c>
+      <c r="H52" s="10">
+        <v>2510</v>
+      </c>
+      <c r="I52" t="s">
+        <v>283</v>
+      </c>
+      <c r="J52" t="s">
+        <v>34</v>
+      </c>
+      <c r="K52" t="s">
+        <v>134</v>
+      </c>
+      <c r="L52" t="s">
+        <v>284</v>
+      </c>
+      <c r="M52" s="10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>285</v>
+      </c>
+      <c r="B53" t="s">
+        <v>280</v>
+      </c>
+      <c r="C53" t="s">
+        <v>286</v>
+      </c>
+      <c r="D53" t="s">
+        <v>287</v>
+      </c>
+      <c r="E53" s="1">
+        <v>45383</v>
+      </c>
+      <c r="F53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="10">
+        <v>908</v>
+      </c>
+      <c r="I53" t="s">
+        <v>288</v>
+      </c>
+      <c r="J53" t="s">
+        <v>80</v>
+      </c>
+      <c r="K53" t="s">
+        <v>39</v>
+      </c>
+      <c r="L53" t="s">
+        <v>289</v>
+      </c>
+      <c r="M53" s="10">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3126,12 +3533,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3364,20 +3773,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7D8E78A-C06A-41E3-81BB-050BD45B738F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C39BF036-B4AC-4393-9990-793AE5FB9BA5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
+    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3402,12 +3812,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C39BF036-B4AC-4393-9990-793AE5FB9BA5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7D8E78A-C06A-41E3-81BB-050BD45B738F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
-    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>